--- a/paper/tables/final/Tabela_3_painel_B.xlsx
+++ b/paper/tables/final/Tabela_3_painel_B.xlsx
@@ -77,7 +77,7 @@
     <t xml:space="preserve">A &gt; C &gt; B </t>
   </si>
   <si>
-    <t>Fonte: Mais Retorno (relatórios PDF exportados; licença comercial).</t>
+    <t>Fonte: Mais Retorno (relatórios PDF exportados; uso acadêmico autorizado).</t>
   </si>
   <si>
     <t>Nota: A, B e C referem-se aos Portfólios A, B e C. A ordenação é do maior para o menor CAGR em cada snapshot. “Estável?” indica ordenação idêntica em D0, D-6m e D-12m.</t>
